--- a/95_Excel/Excel_Begynder_Opgaver.xlsx
+++ b/95_Excel/Excel_Begynder_Opgaver.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulsc\OneDrive - AspIT - Ondrive\Uli\Python\AspIT_Python\95_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84156E6B-7A33-4B46-9CEB-DF4644DBDB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD05A3D5-F301-4C8D-B093-8EE2EB228C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opgave 1 Navn og alder" sheetId="1" r:id="rId1"/>
+    <sheet name="1 Formatering" sheetId="1" r:id="rId1"/>
     <sheet name="Opgave 2 Sum" sheetId="2" r:id="rId2"/>
     <sheet name="Opgave 3 Gennemsnit" sheetId="3" r:id="rId3"/>
     <sheet name="Opgave 4 Fed og kursiv" sheetId="4" r:id="rId4"/>
@@ -210,9 +210,6 @@
     <t>Klaus</t>
   </si>
   <si>
-    <t>Lav en lignende tabel til højre.</t>
-  </si>
-  <si>
     <t>Tast nogle navne og tal ind.</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>Brug disse ikoner til at farve teksten eller baggrunden:</t>
+  </si>
+  <si>
+    <t>Lav en lignende tabel til højre:</t>
   </si>
 </sst>
 </file>
@@ -459,13 +459,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>47775</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>112452</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -503,13 +503,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>137234</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>68628</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -591,13 +591,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>607832</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>144838</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -919,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="4" customWidth="1"/>
@@ -968,13 +968,13 @@
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1018,22 +1018,22 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C23" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C24" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C28" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C32" s="4" t="s">
-        <v>57</v>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1243,7 @@
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/95_Excel/Excel_Begynder_Opgaver.xlsx
+++ b/95_Excel/Excel_Begynder_Opgaver.xlsx
@@ -8,31 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulsc\OneDrive - AspIT - Ondrive\Uli\Python\AspIT_Python\95_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD05A3D5-F301-4C8D-B093-8EE2EB228C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AB8C51-30E3-4DEE-8C49-1248E9604F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Formatering" sheetId="1" r:id="rId1"/>
-    <sheet name="Opgave 2 Sum" sheetId="2" r:id="rId2"/>
-    <sheet name="Opgave 3 Gennemsnit" sheetId="3" r:id="rId3"/>
-    <sheet name="Opgave 4 Fed og kursiv" sheetId="4" r:id="rId4"/>
-    <sheet name="Opgave 5 Farver" sheetId="5" r:id="rId5"/>
-    <sheet name="Opgave 6 Rammer" sheetId="6" r:id="rId6"/>
-    <sheet name="Opgave 7 MIN og MAX" sheetId="7" r:id="rId7"/>
-    <sheet name="Opgave 8 Addition" sheetId="8" r:id="rId8"/>
-    <sheet name="Opgave 9 Subtraktion" sheetId="9" r:id="rId9"/>
-    <sheet name="Opgave 10 Multiplikation" sheetId="10" r:id="rId10"/>
-    <sheet name="Opgave 11 Division" sheetId="11" r:id="rId11"/>
-    <sheet name="Opgave 12 Autofyld" sheetId="12" r:id="rId12"/>
-    <sheet name="Opgave 13 Justering" sheetId="13" r:id="rId13"/>
-    <sheet name="Opgave 14 Skrifttype" sheetId="14" r:id="rId14"/>
-    <sheet name="Opgave 15 Dato" sheetId="15" r:id="rId15"/>
-    <sheet name="Opgave 16 Sortering" sheetId="16" r:id="rId16"/>
-    <sheet name="Opgave 17 Filter" sheetId="17" r:id="rId17"/>
-    <sheet name="Opgave 18 Procent" sheetId="18" r:id="rId18"/>
-    <sheet name="Opgave 19 Graf" sheetId="19" r:id="rId19"/>
-    <sheet name="Opgave 20 Gem fil" sheetId="20" r:id="rId20"/>
+    <sheet name="2 Sum" sheetId="21" r:id="rId2"/>
+    <sheet name="Opgave 2 Sum" sheetId="2" r:id="rId3"/>
+    <sheet name="Opgave 3 Gennemsnit" sheetId="3" r:id="rId4"/>
+    <sheet name="Opgave 4 Fed og kursiv" sheetId="4" r:id="rId5"/>
+    <sheet name="Opgave 5 Farver" sheetId="5" r:id="rId6"/>
+    <sheet name="Opgave 6 Rammer" sheetId="6" r:id="rId7"/>
+    <sheet name="Opgave 7 MIN og MAX" sheetId="7" r:id="rId8"/>
+    <sheet name="Opgave 8 Addition" sheetId="8" r:id="rId9"/>
+    <sheet name="Opgave 9 Subtraktion" sheetId="9" r:id="rId10"/>
+    <sheet name="Opgave 10 Multiplikation" sheetId="10" r:id="rId11"/>
+    <sheet name="Opgave 11 Division" sheetId="11" r:id="rId12"/>
+    <sheet name="Opgave 12 Autofyld" sheetId="12" r:id="rId13"/>
+    <sheet name="Opgave 13 Justering" sheetId="13" r:id="rId14"/>
+    <sheet name="Opgave 14 Skrifttype" sheetId="14" r:id="rId15"/>
+    <sheet name="Opgave 15 Dato" sheetId="15" r:id="rId16"/>
+    <sheet name="Opgave 16 Sortering" sheetId="16" r:id="rId17"/>
+    <sheet name="Opgave 17 Filter" sheetId="17" r:id="rId18"/>
+    <sheet name="Opgave 18 Procent" sheetId="18" r:id="rId19"/>
+    <sheet name="Opgave 19 Graf" sheetId="19" r:id="rId20"/>
+    <sheet name="Opgave 20 Gem fil" sheetId="20" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
   <si>
     <t>Navn</t>
   </si>
@@ -226,6 +227,48 @@
   </si>
   <si>
     <t>Lav en lignende tabel til højre:</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>Indbyggere</t>
+  </si>
+  <si>
+    <t>Frankrig</t>
+  </si>
+  <si>
+    <t>Spanien</t>
+  </si>
+  <si>
+    <t>Italien</t>
+  </si>
+  <si>
+    <t>Sverige</t>
+  </si>
+  <si>
+    <t>Norge</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Sæt nogle af teksterne i fed skrift.</t>
+  </si>
+  <si>
+    <t>Hvor det giver mening:</t>
+  </si>
+  <si>
+    <t>Farvelæg baggrunden i nogle celler.</t>
+  </si>
+  <si>
+    <t>Juster tekstens placering ved hjælp af disse ikoner</t>
+  </si>
+  <si>
+    <t>Tilpas tabellen til højre i overensstemmelse med ovenstående tabel.</t>
   </si>
 </sst>
 </file>
@@ -259,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +321,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -416,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -436,6 +485,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,6 +689,55 @@
         <a:xfrm>
           <a:off x="777240" y="6012180"/>
           <a:ext cx="981212" cy="419158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7843</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Billede 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0655245-39B8-5F35-9F1A-0573B3241FE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1211580" y="2446020"/>
+          <a:ext cx="1600423" cy="895475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1044,6 +1159,47 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <f>A1-A2</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1084,7 +1240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1125,7 +1281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1165,7 +1321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1200,7 +1356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1235,7 +1391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1243,7 +1399,7 @@
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -1271,7 +1427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1311,7 +1467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1357,7 +1513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1398,7 +1554,280 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF132E0-CF31-4B93-8040-A6D3D0BBFE67}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="4.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="12.109375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E2" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="E3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="8">
+        <v>68.5</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="18">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="10">
+        <v>48.6</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="20">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="12">
+        <v>58.7</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="22">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E6" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="16">
+        <f>SUM(F3:F5)</f>
+        <v>175.8</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="22"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="23" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="27" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="31" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="32" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1444,7 +1873,47 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1490,47 +1959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1571,7 +2000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1606,7 +2035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1646,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1697,7 +2126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1739,7 +2168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1778,45 +2207,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <f>A1-A2</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/95_Excel/Excel_Begynder_Opgaver.xlsx
+++ b/95_Excel/Excel_Begynder_Opgaver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulsc\OneDrive - AspIT - Ondrive\Uli\Python\AspIT_Python\95_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D47566-BB20-4987-A208-9F974E327CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0A2966-7768-40F2-B586-8BB4E4B09E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Formatering" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Navn</t>
   </si>
@@ -152,13 +152,19 @@
   </si>
   <si>
     <t>Graf/Diagramm</t>
+  </si>
+  <si>
+    <t>Nur Werte/Formate/Formel einfuegen</t>
+  </si>
+  <si>
+    <t>Transponieren</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,8 +195,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="ADLaM Display"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,8 +226,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -349,11 +366,202 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -373,25 +581,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,7 +639,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>47775</xdr:colOff>
+      <xdr:colOff>41425</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>112452</xdr:rowOff>
     </xdr:to>
@@ -464,9 +683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>137234</xdr:colOff>
+      <xdr:colOff>148664</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>68628</xdr:rowOff>
+      <xdr:rowOff>72438</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -508,9 +727,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>788923</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>93628</xdr:rowOff>
+      <xdr:colOff>796543</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40288</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -554,7 +773,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>607832</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>144838</xdr:rowOff>
+      <xdr:rowOff>148648</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -982,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="2" customWidth="1"/>
@@ -992,18 +1211,20 @@
     <col min="7" max="7" width="12.109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K2" s="26"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="C3" s="5" t="s">
         <v>2</v>
@@ -1011,54 +1232,85 @@
       <c r="D3" s="6">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K3" s="28"/>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="8">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="10">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K5" s="30"/>
+      <c r="L5" s="31"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K10" s="32"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="34"/>
+    </row>
+    <row r="11" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K11" s="35"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="37"/>
+    </row>
+    <row r="12" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K12" s="35"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="37"/>
+    </row>
+    <row r="13" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K13" s="35"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="37"/>
+    </row>
+    <row r="14" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K14" s="38"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="40"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1124,7 +1376,6 @@
     <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
     <col min="10" max="10" width="11.21875" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -1208,7 +1459,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1271,115 +1522,96 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultColWidth="36.5546875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36.5546875" style="28"/>
-    <col min="2" max="16384" width="36.5546875" style="26"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+    <row r="6" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
+    <row r="9" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="27"/>
-    </row>
-    <row r="10" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
+    </row>
+    <row r="10" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+    <row r="11" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
+    <row r="12" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-    </row>
-    <row r="14" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-    </row>
-    <row r="15" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
-    </row>
-    <row r="16" spans="1:2" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29"/>
-    </row>
-    <row r="17" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
-    </row>
-    <row r="18" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
-    </row>
-    <row r="19" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="29"/>
-    </row>
-    <row r="20" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
-    </row>
-    <row r="21" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-    </row>
-    <row r="23" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-    </row>
-    <row r="27" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-    </row>
-    <row r="31" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-    </row>
-    <row r="32" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-    </row>
-    <row r="33" spans="1:1" s="26" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
+    <row r="13" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25"/>
+    </row>
+    <row r="16" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25"/>
+    </row>
+    <row r="17" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25"/>
+    </row>
+    <row r="18" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25"/>
+    </row>
+    <row r="19" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25"/>
+    </row>
+    <row r="20" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/95_Excel/Excel_Begynder_Opgaver.xlsx
+++ b/95_Excel/Excel_Begynder_Opgaver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulsc\OneDrive - AspIT - Ondrive\Uli\Python\AspIT_Python\95_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0A2966-7768-40F2-B586-8BB4E4B09E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0719422-5A0E-4CD5-99CC-CC6D8ECE36D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Formatering" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>Navn</t>
   </si>
@@ -157,14 +157,23 @@
     <t>Nur Werte/Formate/Formel einfuegen</t>
   </si>
   <si>
-    <t>Transponieren</t>
+    <t>Markér flere celler (med musen eller ved at holde &lt;Shift&gt; nede og bruge piletasterne).</t>
+  </si>
+  <si>
+    <t>På den måde kan du ændre formateringen af mange celler på én gang.</t>
+  </si>
+  <si>
+    <t>I stedet for at klikke på ikonerne kan du også bruge  &lt;CTRL&gt; + 1 til at få adgang til alle formateringsfunktioner.</t>
+  </si>
+  <si>
+    <t>MIDDEL(B15:B16)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,13 +204,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="ADLaM Display"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,14 +230,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -428,140 +426,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -602,15 +471,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,8 +588,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>796543</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>40288</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>86008</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1201,20 +1061,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" style="2" customWidth="1"/>
     <col min="3" max="4" width="8.88671875" style="2"/>
     <col min="5" max="6" width="12.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="59.109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1084,7 @@
       <c r="K2" s="26"/>
       <c r="L2" s="27"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="C3" s="5" t="s">
         <v>2</v>
@@ -1235,7 +1095,7 @@
       <c r="K3" s="28"/>
       <c r="L3" s="29"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
@@ -1245,7 +1105,7 @@
       <c r="K4" s="28"/>
       <c r="L4" s="29"/>
     </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
@@ -1255,62 +1115,37 @@
       <c r="K5" s="30"/>
       <c r="L5" s="31"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="34"/>
-    </row>
-    <row r="11" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="37"/>
-    </row>
-    <row r="12" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="37"/>
-    </row>
-    <row r="13" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="37"/>
-    </row>
-    <row r="14" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="40"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1353,6 +1188,21 @@
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1592,7 +1442,7 @@
     </row>
     <row r="14" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
